--- a/results/intensive_baseline_weighted/permutations/log_intensive_baseline_weighted_b1_1000perm.xlsx
+++ b/results/intensive_baseline_weighted/permutations/log_intensive_baseline_weighted_b1_1000perm.xlsx
@@ -372,7 +372,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ver</t>
+          <t>verifiability</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
